--- a/public/template-ruangan.xlsx
+++ b/public/template-ruangan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\diakademik\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3471AA-68C6-4846-9F42-4CA3366A532D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA1C347-30CA-416C-BA39-5C7635539B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{352E3735-C2E0-439F-886B-526F4739CD28}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7360" xr2:uid="{352E3735-C2E0-439F-886B-526F4739CD28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,8 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -61,15 +58,6 @@
     <t>Status Aktif</t>
   </si>
   <si>
-    <t>Ruang Koperasi</t>
-  </si>
-  <si>
-    <t>Gedung D</t>
-  </si>
-  <si>
-    <t>SMP YPM 1 Taman</t>
-  </si>
-  <si>
     <t>KO11</t>
   </si>
   <si>
@@ -83,6 +71,15 @@
   </si>
   <si>
     <t>KO12</t>
+  </si>
+  <si>
+    <t>KBM</t>
+  </si>
+  <si>
+    <t>LANTAI 1 SMK YPM 3</t>
+  </si>
+  <si>
+    <t>SEKOLAH</t>
   </si>
 </sst>
 </file>
@@ -145,7 +142,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -445,7 +442,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.453125" bestFit="1" customWidth="1"/>
@@ -482,16 +479,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -500,24 +497,24 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>25</v>
@@ -526,10 +523,10 @@
         <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
